--- a/docs/templates/customer_import_template.xlsx
+++ b/docs/templates/customer_import_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="客户导入" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户导入" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'客户导入'!$A$1:$S$1</definedName>
@@ -558,7 +558,7 @@
     <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否,Y,N,true,false,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
+    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>

--- a/docs/templates/customer_import_template.xlsx
+++ b/docs/templates/customer_import_template.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
@@ -460,90 +460,95 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>业务模式</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>区域</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>城市</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>地址</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>X轴描述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>X轴评分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Y轴描述</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Y轴评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Z轴描述</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Z轴评分</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>客户策略</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>潜在贡献</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>联系人姓名</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>联系人职位</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>联系人电话</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>联系人邮箱</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>是否关键人</t>
         </is>
@@ -555,10 +560,10 @@
     <dataValidation sqref="B2:B5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Hunting,Farming"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"是,否,Y,N,true,false,1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="G2:G5000 I2:I5000 K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
